--- a/カテゴリ.xlsx
+++ b/カテゴリ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lon\Desktop\SpringOuyo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C12E3F88-84D0-4485-B08B-2293EEFC8DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FD7B279-2054-4085-9406-4D357A4E68E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2664" yWindow="420" windowWidth="17916" windowHeight="11592" xr2:uid="{0244B7D2-F854-422F-957C-616BE396D2DA}"/>
+    <workbookView xWindow="3492" yWindow="1608" windowWidth="17280" windowHeight="8964" xr2:uid="{0244B7D2-F854-422F-957C-616BE396D2DA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="44">
   <si>
     <t>分類番号</t>
     <rPh sb="0" eb="4">
@@ -65,13 +65,209 @@
       <t>ショウブンルイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>教材・学業関連</t>
+  </si>
+  <si>
+    <r>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>・タブレット・スマホ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>その他</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>一人暮らし応援・日用品</t>
+  </si>
+  <si>
+    <t>趣味・エンタメ</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ハンドメイド・その他</t>
+    </r>
+  </si>
+  <si>
+    <t>ファッション・衣類</t>
+  </si>
+  <si>
+    <t>教材、学業関連</t>
+    <rPh sb="0" eb="2">
+      <t>キョウザイ</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>ガクギョウカンレン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前学期の専門書や語学テキスト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>教科書</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>参考書</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>資格試験（TOEIC、ITパスポートなど）の対策本</t>
+  </si>
+  <si>
+    <t>文房具</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>余ったノート、ルーズリーフ、未使用のペン</t>
+  </si>
+  <si>
+    <t>私服</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サイズが合わなくなった服、流行の古着</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バッグ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>通学用リュック、トートバッグ</t>
+  </si>
+  <si>
+    <t>就活スーツ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リクルートスーツ、ネクタイ、パンプス</t>
+  </si>
+  <si>
+    <t>サークルや学園祭で一度だけ使ったコスプレ・ドレス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実家から送られてきて余ったレトルト食品や洗剤</t>
+  </si>
+  <si>
+    <t>衣装</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小型家電</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ケトル、ドライヤー、ミニ扇風機、卓上ライト</t>
+  </si>
+  <si>
+    <t>キッチン用品</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マグカップ、お皿、未使用の調理器具</t>
+  </si>
+  <si>
+    <t>インテリア</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>収納ボックス、クッション、ポスター</t>
+  </si>
+  <si>
+    <t>消耗品</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>本・マンガ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>読み終えた小説、コミック全巻セット</t>
+  </si>
+  <si>
+    <r>
+      <t>ゲーム・</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>CD</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>遊ばなくなったゲームソフト、周辺機器</t>
+  </si>
+  <si>
+    <t>サークル関連</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>楽器、テニスラケット、スニーカー</t>
+  </si>
+  <si>
+    <t>手作り雑貨</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アクセサリー、布小物、ステッカー</t>
+  </si>
+  <si>
+    <t>おまけ・試供品</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>化粧品のサンプル、ガチャガチャの景品</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -86,6 +282,21 @@
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -110,9 +321,21 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -428,13 +651,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D4B8B7B-A9F0-4E9C-8B1C-8FDD43851D85}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14.8984375" customWidth="1"/>
-    <col min="2" max="2" width="25.796875" customWidth="1"/>
-    <col min="3" max="3" width="20.19921875" customWidth="1"/>
-    <col min="4" max="4" width="30.296875" customWidth="1"/>
+    <col min="2" max="2" width="24.09765625" customWidth="1"/>
+    <col min="3" max="3" width="54.296875" customWidth="1"/>
+    <col min="4" max="4" width="44.09765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
@@ -450,6 +673,241 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="19.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="19.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="19.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="28.8" x14ac:dyDescent="0.45">
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B25" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/カテゴリ.xlsx
+++ b/カテゴリ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lon\Desktop\SpringOuyo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FD7B279-2054-4085-9406-4D357A4E68E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55C4DB38-6794-480A-BDA5-0E860EF2D326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3492" yWindow="1608" windowWidth="17280" windowHeight="8964" xr2:uid="{0244B7D2-F854-422F-957C-616BE396D2DA}"/>
+    <workbookView xWindow="1668" yWindow="1584" windowWidth="17280" windowHeight="8964" xr2:uid="{0244B7D2-F854-422F-957C-616BE396D2DA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -783,7 +783,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="28.8" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" ht="19.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>

--- a/カテゴリ.xlsx
+++ b/カテゴリ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lon\Desktop\SpringOuyo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55C4DB38-6794-480A-BDA5-0E860EF2D326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1C451E2-AA9B-4881-B211-12B69D35B995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1668" yWindow="1584" windowWidth="17280" windowHeight="8964" xr2:uid="{0244B7D2-F854-422F-957C-616BE396D2DA}"/>
+    <workbookView xWindow="12" yWindow="1104" windowWidth="20028" windowHeight="11592" xr2:uid="{0244B7D2-F854-422F-957C-616BE396D2DA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -675,6 +675,9 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2">
+        <v>101</v>
+      </c>
       <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
@@ -683,6 +686,9 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="19.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3">
+        <v>102</v>
+      </c>
       <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
@@ -694,6 +700,9 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>103</v>
+      </c>
       <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
@@ -705,6 +714,9 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="19.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>104</v>
+      </c>
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
@@ -716,6 +728,9 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>105</v>
+      </c>
       <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
@@ -724,6 +739,9 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>106</v>
+      </c>
       <c r="B7" s="1" t="s">
         <v>11</v>
       </c>
@@ -732,6 +750,9 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>201</v>
+      </c>
       <c r="B8" s="2" t="s">
         <v>10</v>
       </c>
@@ -740,6 +761,9 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9">
+        <v>202</v>
+      </c>
       <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
@@ -751,6 +775,9 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A10">
+        <v>203</v>
+      </c>
       <c r="B10" s="2" t="s">
         <v>10</v>
       </c>
@@ -762,6 +789,9 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A11">
+        <v>204</v>
+      </c>
       <c r="B11" s="2" t="s">
         <v>10</v>
       </c>
@@ -773,6 +803,9 @@
       </c>
     </row>
     <row r="12" spans="1:4" ht="19.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12">
+        <v>205</v>
+      </c>
       <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
@@ -784,6 +817,9 @@
       </c>
     </row>
     <row r="13" spans="1:4" ht="19.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A13">
+        <v>301</v>
+      </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
@@ -792,6 +828,9 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A14">
+        <v>302</v>
+      </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
@@ -803,6 +842,9 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A15">
+        <v>303</v>
+      </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
@@ -814,6 +856,9 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A16">
+        <v>304</v>
+      </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
@@ -824,7 +869,10 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A17">
+        <v>305</v>
+      </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
@@ -835,7 +883,10 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A18">
+        <v>401</v>
+      </c>
       <c r="B18" s="1" t="s">
         <v>8</v>
       </c>
@@ -843,7 +894,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A19">
+        <v>402</v>
+      </c>
       <c r="B19" s="1" t="s">
         <v>8</v>
       </c>
@@ -854,7 +908,10 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A20">
+        <v>403</v>
+      </c>
       <c r="B20" s="1" t="s">
         <v>8</v>
       </c>
@@ -865,7 +922,10 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A21">
+        <v>404</v>
+      </c>
       <c r="B21" s="1" t="s">
         <v>8</v>
       </c>
@@ -876,7 +936,10 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A22">
+        <v>405</v>
+      </c>
       <c r="B22" s="1" t="s">
         <v>8</v>
       </c>
@@ -884,7 +947,10 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A23">
+        <v>406</v>
+      </c>
       <c r="B23" s="1" t="s">
         <v>8</v>
       </c>
@@ -895,7 +961,10 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A24">
+        <v>407</v>
+      </c>
       <c r="B24" s="1" t="s">
         <v>8</v>
       </c>
@@ -906,7 +975,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B25" s="1"/>
     </row>
   </sheetData>
